--- a/artfynd/A 32325-2024 artfynd.xlsx
+++ b/artfynd/A 32325-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>120852624</v>
       </c>
       <c r="B2" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>120852629</v>
       </c>
       <c r="B3" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>120852625</v>
       </c>
       <c r="B4" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120852627</v>
+        <v>120852628</v>
       </c>
       <c r="B5" t="n">
-        <v>98071</v>
+        <v>79718</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>798913</v>
+        <v>798880</v>
       </c>
       <c r="R5" t="n">
-        <v>7320364</v>
+        <v>7320238</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120852626</v>
+        <v>120852741</v>
       </c>
       <c r="B6" t="n">
-        <v>82382</v>
+        <v>79586</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>6456</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>799004</v>
+        <v>798969</v>
       </c>
       <c r="R6" t="n">
-        <v>7320348</v>
+        <v>7320330</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120852628</v>
+        <v>120852626</v>
       </c>
       <c r="B7" t="n">
-        <v>79715</v>
+        <v>82385</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,25 +1217,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6464</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>798880</v>
+        <v>799004</v>
       </c>
       <c r="R7" t="n">
-        <v>7320238</v>
+        <v>7320348</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120852741</v>
+        <v>120852627</v>
       </c>
       <c r="B8" t="n">
-        <v>79583</v>
+        <v>98081</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,25 +1323,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>798969</v>
+        <v>798913</v>
       </c>
       <c r="R8" t="n">
-        <v>7320330</v>
+        <v>7320364</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 32325-2024 artfynd.xlsx
+++ b/artfynd/A 32325-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120852624</v>
+        <v>120852629</v>
       </c>
       <c r="B2" t="n">
-        <v>98081</v>
+        <v>78601</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>798877</v>
+        <v>798830</v>
       </c>
       <c r="R2" t="n">
-        <v>7320372</v>
+        <v>7320289</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120852629</v>
+        <v>120852625</v>
       </c>
       <c r="B3" t="n">
-        <v>78601</v>
+        <v>98081</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>798830</v>
+        <v>798864</v>
       </c>
       <c r="R3" t="n">
-        <v>7320289</v>
+        <v>7320388</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120852625</v>
+        <v>120852741</v>
       </c>
       <c r="B4" t="n">
-        <v>98081</v>
+        <v>79586</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>798864</v>
+        <v>798969</v>
       </c>
       <c r="R4" t="n">
-        <v>7320388</v>
+        <v>7320330</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120852628</v>
+        <v>120852626</v>
       </c>
       <c r="B5" t="n">
-        <v>79718</v>
+        <v>82385</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>798880</v>
+        <v>799004</v>
       </c>
       <c r="R5" t="n">
-        <v>7320238</v>
+        <v>7320348</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120852741</v>
+        <v>120852624</v>
       </c>
       <c r="B6" t="n">
-        <v>79586</v>
+        <v>98081</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>798969</v>
+        <v>798877</v>
       </c>
       <c r="R6" t="n">
-        <v>7320330</v>
+        <v>7320372</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120852626</v>
+        <v>120852628</v>
       </c>
       <c r="B7" t="n">
-        <v>82385</v>
+        <v>79718</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,25 +1217,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>6464</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>799004</v>
+        <v>798880</v>
       </c>
       <c r="R7" t="n">
-        <v>7320348</v>
+        <v>7320238</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 32325-2024 artfynd.xlsx
+++ b/artfynd/A 32325-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120852629</v>
+        <v>120852626</v>
       </c>
       <c r="B2" t="n">
-        <v>78601</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>798830</v>
+        <v>799004</v>
       </c>
       <c r="R2" t="n">
-        <v>7320289</v>
+        <v>7320348</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120852625</v>
+        <v>120852629</v>
       </c>
       <c r="B3" t="n">
-        <v>98081</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>798864</v>
+        <v>798830</v>
       </c>
       <c r="R3" t="n">
-        <v>7320388</v>
+        <v>7320289</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,12 +880,7 @@
         <v>120852741</v>
       </c>
       <c r="B4" t="n">
-        <v>79586</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,37 +978,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120852626</v>
+        <v>120852628</v>
       </c>
       <c r="B5" t="n">
-        <v>82385</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>6464</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>799004</v>
+        <v>798880</v>
       </c>
       <c r="R5" t="n">
-        <v>7320348</v>
+        <v>7320238</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1102,12 +1082,7 @@
         <v>120852624</v>
       </c>
       <c r="B6" t="n">
-        <v>98081</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1205,37 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120852628</v>
+        <v>120852625</v>
       </c>
       <c r="B7" t="n">
-        <v>79718</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>798880</v>
+        <v>798864</v>
       </c>
       <c r="R7" t="n">
-        <v>7320238</v>
+        <v>7320388</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,12 +1284,7 @@
         <v>120852627</v>
       </c>
       <c r="B8" t="n">
-        <v>98081</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 32325-2024 artfynd.xlsx
+++ b/artfynd/A 32325-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Sweco naturvärdesinventering och artinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120852626</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Sweco naturvärdesinventering och artinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120852629</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Sweco naturvärdesinventering och artinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120852741</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Sweco naturvärdesinventering och artinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120852628</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Sweco naturvärdesinventering och artinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120852624</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>Sweco naturvärdesinventering och artinventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120852625</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,8 +1414,22 @@
           <t>Sweco naturvärdesinventering och artinventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120852627</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>